--- a/keywords.xlsx
+++ b/keywords.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chong\Nutstore\1\Text opensource\figs\fig1\keywords\关键词频次统计 - 英文\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="关键词明细" sheetId="1" r:id="rId1"/>
-    <sheet name="子类汇总" sheetId="2" r:id="rId2"/>
-    <sheet name="大类汇总" sheetId="3" r:id="rId3"/>
+    <sheet name="keywords" sheetId="1" r:id="rId1"/>
+    <sheet name="Subclass summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Superclass summary" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,25 +36,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="122">
   <si>
-    <t>大类</t>
-  </si>
-  <si>
-    <t>子类</t>
-  </si>
-  <si>
-    <t>关键词(英文)</t>
-  </si>
-  <si>
-    <t>命中次数</t>
-  </si>
-  <si>
-    <t>占比(命中/总数)</t>
-  </si>
-  <si>
-    <t>水系统</t>
-  </si>
-  <si>
-    <t>供水</t>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Subcategory</t>
+  </si>
+  <si>
+    <t>Keyword (English)</t>
+  </si>
+  <si>
+    <t>Hits</t>
+  </si>
+  <si>
+    <t>Proportion (Hits/Total)</t>
+  </si>
+  <si>
+    <t>Water Systems</t>
+  </si>
+  <si>
+    <t>Water Supply</t>
   </si>
   <si>
     <t>water distribution</t>
@@ -58,7 +63,7 @@
     <t>water supply</t>
   </si>
   <si>
-    <t>排水</t>
+    <t>Drainage</t>
   </si>
   <si>
     <t>sewer</t>
@@ -73,7 +78,7 @@
     <t>storm water</t>
   </si>
   <si>
-    <t>湖泊河流</t>
+    <t>Lakes &amp; Rivers</t>
   </si>
   <si>
     <t>river</t>
@@ -94,7 +99,7 @@
     <t>stream</t>
   </si>
   <si>
-    <t>海洋</t>
+    <t>Marine</t>
   </si>
   <si>
     <t>coastal</t>
@@ -109,7 +114,7 @@
     <t>sea</t>
   </si>
   <si>
-    <t>污水处理</t>
+    <t>Wastewater Treatment</t>
   </si>
   <si>
     <t>wastewater</t>
@@ -121,7 +126,7 @@
     <t>sewage</t>
   </si>
   <si>
-    <t>饮用水处理</t>
+    <t>Drinking Water Treatment</t>
   </si>
   <si>
     <t>drinking water</t>
@@ -133,13 +138,13 @@
     <t>potable water</t>
   </si>
   <si>
-    <t>溢流</t>
+    <t>Overflow</t>
   </si>
   <si>
     <t>overflow</t>
   </si>
   <si>
-    <t>内涝</t>
+    <t>Waterlogging</t>
   </si>
   <si>
     <t>flood</t>
@@ -151,7 +156,7 @@
     <t>waterlogging</t>
   </si>
   <si>
-    <t>水污染</t>
+    <t>Water Pollution</t>
   </si>
   <si>
     <t>water quality</t>
@@ -169,7 +174,7 @@
     <t>AI</t>
   </si>
   <si>
-    <t>机器学习</t>
+    <t>Machine Learning</t>
   </si>
   <si>
     <t>machine learning</t>
@@ -184,7 +189,7 @@
     <t>gradient boosting</t>
   </si>
   <si>
-    <t>深度学习</t>
+    <t>Deep Learning</t>
   </si>
   <si>
     <t>deep learning</t>
@@ -214,16 +219,16 @@
     <t>RNN</t>
   </si>
   <si>
-    <t>强化学习</t>
+    <t>Reinforcement Learning</t>
   </si>
   <si>
     <t>reinforcement learning</t>
   </si>
   <si>
-    <t>工程技术</t>
-  </si>
-  <si>
-    <t>供水管网漏损</t>
+    <t>Engineering Technology</t>
+  </si>
+  <si>
+    <t>Pipe Network Leakage</t>
   </si>
   <si>
     <t>leak</t>
@@ -238,7 +243,7 @@
     <t>burst detection</t>
   </si>
   <si>
-    <t>污水处理技术</t>
+    <t>Wastewater Treatment Technology</t>
   </si>
   <si>
     <t>wastewater treatment plant</t>
@@ -256,7 +261,7 @@
     <t>WWTP</t>
   </si>
   <si>
-    <t>实时控制</t>
+    <t>Real-time Control</t>
   </si>
   <si>
     <t>real-time control</t>
@@ -268,7 +273,7 @@
     <t>RTC</t>
   </si>
   <si>
-    <t>系统预测</t>
+    <t>System Prediction</t>
   </si>
   <si>
     <t>prediction</t>
@@ -283,7 +288,7 @@
     <t>forecast</t>
   </si>
   <si>
-    <t>系统模拟</t>
+    <t>System Simulation</t>
   </si>
   <si>
     <t>simulation</t>
@@ -295,7 +300,7 @@
     <t>digital twin</t>
   </si>
   <si>
-    <t>系统优化</t>
+    <t>System Optimization</t>
   </si>
   <si>
     <t>optimization</t>
@@ -316,7 +321,7 @@
     <t>metaheuristic</t>
   </si>
   <si>
-    <t>建模</t>
+    <t>Modeling</t>
   </si>
   <si>
     <t>modeling</t>
@@ -325,10 +330,10 @@
     <t>calibration</t>
   </si>
   <si>
-    <t>命中论文数(去重)</t>
-  </si>
-  <si>
-    <t>备注</t>
+    <t>Papers Hit (deduplicated)</t>
+  </si>
+  <si>
+    <t>Note</t>
   </si>
   <si>
     <t>11.96%</t>
@@ -355,7 +360,7 @@
     <t>2.24%</t>
   </si>
   <si>
-    <t>v2新增</t>
+    <t>v2 added</t>
   </si>
   <si>
     <t>24.78%</t>
@@ -364,7 +369,7 @@
     <t>30.88%</t>
   </si>
   <si>
-    <t>v3新增</t>
+    <t>v3 added</t>
   </si>
   <si>
     <t>5.73%</t>
@@ -385,7 +390,7 @@
     <t>9.34%</t>
   </si>
   <si>
-    <t>论文总数</t>
+    <t>Total Papers</t>
   </si>
   <si>
     <t>73.60%</t>
@@ -875,148 +880,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
